--- a/testdata/Opencart_Testdata.xlsx
+++ b/testdata/Opencart_Testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahesh\eclipse-workspace\Opencart-CucumberFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84B7A4B-D4B0-4724-ABBE-11B8B3F6E85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30821F4-7267-4704-8EBB-603878D8DF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C25B3EBA-FC6D-4CA0-B815-305889E32E4E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Username</t>
   </si>
@@ -73,22 +73,29 @@
   </si>
   <si>
     <t>jejurkar@gmail.com</t>
+  </si>
+  <si>
+    <t>TcNo</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -102,6 +109,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -144,17 +171,23 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -472,78 +505,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1460DDA0-C385-49BF-98CE-D70BDB864492}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{484442D7-371E-434D-AF96-7C66FB5F3128}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{F651E95C-9EA8-44FC-847D-DD93F2876A0C}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{A4F9863F-0DD0-4A02-9F47-08640AC2ABD2}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{A51801AC-CE80-46A9-A453-E017D9E29F8A}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{E3FCD3F6-4C5F-4D9D-85B1-3795C1DC6771}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{ECEA415C-C029-4572-8FBF-5806B66353F8}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{484442D7-371E-434D-AF96-7C66FB5F3128}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{F651E95C-9EA8-44FC-847D-DD93F2876A0C}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{A4F9863F-0DD0-4A02-9F47-08640AC2ABD2}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{A51801AC-CE80-46A9-A453-E017D9E29F8A}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{E3FCD3F6-4C5F-4D9D-85B1-3795C1DC6771}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{ECEA415C-C029-4572-8FBF-5806B66353F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>